--- a/ClimOO material/materials for implementations /ClimOO Vocabulary.xlsx
+++ b/ClimOO material/materials for implementations /ClimOO Vocabulary.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/ClimOO-Ontology/ClimOO material/materials for implementations /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4697E71-F0FA-0B48-8582-6A9C9CB97D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0E3046-B004-BE45-B859-3E98F69C6162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CB153552-6711-0040-AB62-F0CB02156726}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{CB153552-6711-0040-AB62-F0CB02156726}"/>
   </bookViews>
   <sheets>
     <sheet name="ClimOO Vocabulary" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClimOO Vocabulary'!$A$1:$A$747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClimOO Vocabulary'!$A$1:$A$739</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2248" uniqueCount="753">
   <si>
     <t>FSSMF Pillar (primary pertinence)</t>
   </si>
@@ -2271,6 +2271,33 @@
   </si>
   <si>
     <t>increased seasonality of precipitation</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>ability to access</t>
+  </si>
+  <si>
+    <t>access</t>
+  </si>
+  <si>
+    <t>risk</t>
+  </si>
+  <si>
+    <t>resource role</t>
+  </si>
+  <si>
+    <t>exposure to contaminated environmental material</t>
+  </si>
+  <si>
+    <t>use of a resource</t>
+  </si>
+  <si>
+    <t>access system</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -2682,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05EE52F-6B9B-9646-8D2F-C9D94D87C781}">
-  <dimension ref="A1:D747"/>
+  <dimension ref="A1:E750"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="82.5" bestFit="1" customWidth="1"/>
@@ -5192,2159 +5219,2175 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228" s="3"/>
+      <c r="A228" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C228" t="s">
+        <v>424</v>
+      </c>
+      <c r="D228" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229" s="3"/>
+      <c r="A229" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C229" t="s">
+        <v>424</v>
+      </c>
+      <c r="D229" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C230" t="s">
         <v>424</v>
       </c>
       <c r="D230" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C231" t="s">
         <v>424</v>
       </c>
       <c r="D231" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C232" t="s">
         <v>424</v>
       </c>
       <c r="D232" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C233" t="s">
         <v>424</v>
       </c>
       <c r="D233" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C234" t="s">
         <v>424</v>
       </c>
       <c r="D234" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C235" t="s">
         <v>424</v>
       </c>
       <c r="D235" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C236" t="s">
         <v>424</v>
       </c>
       <c r="D236" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C237" t="s">
         <v>424</v>
       </c>
       <c r="D237" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C238" t="s">
         <v>424</v>
       </c>
       <c r="D238" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C239" t="s">
         <v>424</v>
       </c>
       <c r="D239" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C240" t="s">
         <v>424</v>
       </c>
       <c r="D240" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C241" t="s">
         <v>424</v>
       </c>
       <c r="D241" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C242" t="s">
         <v>424</v>
       </c>
       <c r="D242" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C243" t="s">
         <v>424</v>
       </c>
       <c r="D243" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C244" t="s">
         <v>424</v>
       </c>
       <c r="D244" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C245" t="s">
         <v>424</v>
       </c>
       <c r="D245" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C246" t="s">
         <v>424</v>
       </c>
       <c r="D246" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C247" t="s">
         <v>424</v>
       </c>
       <c r="D247" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C248" t="s">
         <v>424</v>
       </c>
       <c r="D248" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C249" t="s">
         <v>424</v>
       </c>
       <c r="D249" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C250" t="s">
         <v>424</v>
       </c>
       <c r="D250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C251" t="s">
         <v>424</v>
       </c>
       <c r="D251" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C252" t="s">
         <v>424</v>
       </c>
       <c r="D252" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C253" t="s">
         <v>424</v>
       </c>
       <c r="D253" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C254" t="s">
         <v>424</v>
       </c>
       <c r="D254" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C255" t="s">
         <v>424</v>
       </c>
       <c r="D255" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C256" t="s">
         <v>424</v>
       </c>
       <c r="D256" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C257" t="s">
         <v>424</v>
       </c>
       <c r="D257" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C258" t="s">
         <v>424</v>
       </c>
       <c r="D258" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C259" t="s">
         <v>424</v>
       </c>
       <c r="D259" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C260" t="s">
         <v>424</v>
       </c>
       <c r="D260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C261" t="s">
         <v>424</v>
       </c>
       <c r="D261" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C262" t="s">
         <v>424</v>
       </c>
       <c r="D262" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C263" t="s">
         <v>424</v>
       </c>
       <c r="D263" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C264" t="s">
         <v>424</v>
       </c>
       <c r="D264" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C265" t="s">
         <v>424</v>
       </c>
       <c r="D265" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C266" t="s">
         <v>424</v>
       </c>
       <c r="D266" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C267" t="s">
         <v>424</v>
       </c>
       <c r="D267" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C268" t="s">
         <v>424</v>
       </c>
       <c r="D268" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C269" t="s">
         <v>424</v>
       </c>
       <c r="D269" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C270" t="s">
         <v>424</v>
       </c>
       <c r="D270" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C271" t="s">
         <v>424</v>
       </c>
       <c r="D271" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C272" t="s">
         <v>424</v>
       </c>
       <c r="D272" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
-        <v>271</v>
+        <v>493</v>
       </c>
       <c r="C273" t="s">
         <v>424</v>
       </c>
       <c r="D273" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C274" t="s">
         <v>424</v>
       </c>
       <c r="D274" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
-        <v>493</v>
+        <v>274</v>
       </c>
       <c r="C275" t="s">
         <v>424</v>
       </c>
       <c r="D275" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C276" t="s">
         <v>424</v>
       </c>
       <c r="D276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C277" t="s">
         <v>424</v>
       </c>
       <c r="D277" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C278" t="s">
         <v>424</v>
       </c>
       <c r="D278" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C279" t="s">
         <v>424</v>
       </c>
       <c r="D279" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C280" t="s">
         <v>424</v>
       </c>
       <c r="D280" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C281" t="s">
         <v>424</v>
       </c>
       <c r="D281" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C282" t="s">
         <v>424</v>
       </c>
       <c r="D282" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C283" t="s">
         <v>424</v>
       </c>
       <c r="D283" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C284" t="s">
         <v>424</v>
       </c>
       <c r="D284" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C285" t="s">
         <v>424</v>
       </c>
       <c r="D285" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C286" t="s">
         <v>424</v>
       </c>
       <c r="D286" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C287" t="s">
         <v>424</v>
       </c>
       <c r="D287" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C288" t="s">
         <v>424</v>
       </c>
       <c r="D288" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C289" t="s">
         <v>424</v>
       </c>
       <c r="D289" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C290" t="s">
         <v>424</v>
       </c>
       <c r="D290" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C291" t="s">
         <v>424</v>
       </c>
       <c r="D291" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C292" t="s">
         <v>424</v>
       </c>
       <c r="D292" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C293" t="s">
         <v>424</v>
       </c>
       <c r="D293" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C294" t="s">
         <v>424</v>
       </c>
       <c r="D294" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C295" t="s">
         <v>424</v>
       </c>
       <c r="D295" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C296" t="s">
         <v>424</v>
       </c>
       <c r="D296" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C297" t="s">
         <v>424</v>
       </c>
       <c r="D297" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C298" t="s">
         <v>424</v>
       </c>
       <c r="D298" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C299" t="s">
         <v>424</v>
       </c>
       <c r="D299" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C300" t="s">
         <v>424</v>
       </c>
       <c r="D300" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C301" t="s">
         <v>424</v>
       </c>
       <c r="D301" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C302" t="s">
         <v>424</v>
       </c>
       <c r="D302" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C303" t="s">
         <v>424</v>
       </c>
       <c r="D303" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C304" t="s">
         <v>424</v>
       </c>
       <c r="D304" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C305" t="s">
         <v>424</v>
       </c>
       <c r="D305" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C306" t="s">
         <v>424</v>
       </c>
       <c r="D306" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C307" t="s">
         <v>424</v>
       </c>
       <c r="D307" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C308" t="s">
         <v>424</v>
       </c>
       <c r="D308" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C309" t="s">
         <v>424</v>
       </c>
       <c r="D309" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C310" t="s">
         <v>424</v>
       </c>
       <c r="D310" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C311" t="s">
         <v>424</v>
       </c>
       <c r="D311" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C312" t="s">
         <v>424</v>
       </c>
       <c r="D312" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C313" t="s">
         <v>424</v>
       </c>
       <c r="D313" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C314" t="s">
         <v>424</v>
       </c>
       <c r="D314" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C315" t="s">
         <v>424</v>
       </c>
       <c r="D315" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C316" t="s">
         <v>424</v>
       </c>
       <c r="D316" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C317" t="s">
         <v>424</v>
       </c>
       <c r="D317" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C318" t="s">
         <v>424</v>
       </c>
       <c r="D318" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C319" t="s">
         <v>424</v>
       </c>
       <c r="D319" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C320" t="s">
         <v>424</v>
       </c>
       <c r="D320" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C321" t="s">
         <v>424</v>
       </c>
       <c r="D321" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C322" t="s">
         <v>424</v>
       </c>
       <c r="D322" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C323" t="s">
         <v>424</v>
       </c>
       <c r="D323" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C324" t="s">
         <v>424</v>
       </c>
       <c r="D324" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C325" t="s">
         <v>424</v>
       </c>
       <c r="D325" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C326" t="s">
         <v>424</v>
       </c>
       <c r="D326" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C327" t="s">
         <v>424</v>
       </c>
       <c r="D327" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C328" t="s">
         <v>424</v>
       </c>
       <c r="D328" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C329" t="s">
         <v>424</v>
       </c>
       <c r="D329" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C330" t="s">
         <v>424</v>
       </c>
       <c r="D330" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C331" t="s">
         <v>424</v>
       </c>
       <c r="D331" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C332" t="s">
         <v>424</v>
       </c>
       <c r="D332" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C333" t="s">
         <v>424</v>
       </c>
       <c r="D333" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C334" t="s">
         <v>424</v>
       </c>
       <c r="D334" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C335" t="s">
         <v>424</v>
       </c>
       <c r="D335" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A336" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C336" t="s">
         <v>424</v>
       </c>
       <c r="D336" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C337" t="s">
         <v>424</v>
       </c>
       <c r="D337" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C338" t="s">
         <v>424</v>
       </c>
       <c r="D338" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C339" t="s">
         <v>424</v>
       </c>
       <c r="D339" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C340" t="s">
         <v>424</v>
       </c>
       <c r="D340" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C341" t="s">
         <v>424</v>
       </c>
       <c r="D341" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C342" t="s">
         <v>424</v>
       </c>
       <c r="D342" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C343" t="s">
         <v>424</v>
       </c>
       <c r="D343" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C344" t="s">
         <v>424</v>
       </c>
       <c r="D344" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C345" t="s">
         <v>424</v>
       </c>
       <c r="D345" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C346" t="s">
         <v>424</v>
       </c>
       <c r="D346" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C347" t="s">
         <v>424</v>
       </c>
       <c r="D347" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A348" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C348" t="s">
         <v>424</v>
       </c>
       <c r="D348" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A349" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C349" t="s">
         <v>424</v>
       </c>
       <c r="D349" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C350" t="s">
         <v>424</v>
       </c>
       <c r="D350" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C351" t="s">
         <v>424</v>
       </c>
       <c r="D351" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C352" t="s">
         <v>424</v>
       </c>
       <c r="D352" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C353" t="s">
         <v>424</v>
       </c>
       <c r="D353" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C354" t="s">
         <v>424</v>
       </c>
       <c r="D354" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C355" t="s">
         <v>424</v>
       </c>
       <c r="D355" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A356" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C356" t="s">
         <v>424</v>
       </c>
       <c r="D356" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A357" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C357" t="s">
         <v>424</v>
       </c>
       <c r="D357" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A358" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C358" t="s">
         <v>424</v>
       </c>
       <c r="D358" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A359" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C359" t="s">
         <v>424</v>
       </c>
       <c r="D359" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A360" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C360" t="s">
         <v>424</v>
       </c>
       <c r="D360" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C361" t="s">
         <v>424</v>
       </c>
       <c r="D361" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A362" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C362" t="s">
         <v>424</v>
       </c>
       <c r="D362" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C363" t="s">
         <v>424</v>
       </c>
       <c r="D363" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C364" t="s">
         <v>424</v>
       </c>
       <c r="D364" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A365" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C365" t="s">
         <v>424</v>
       </c>
       <c r="D365" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A366" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C366" t="s">
         <v>424</v>
       </c>
       <c r="D366" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C367" t="s">
         <v>424</v>
       </c>
       <c r="D367" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A368" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C368" t="s">
         <v>424</v>
       </c>
       <c r="D368" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A369" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C369" t="s">
         <v>424</v>
       </c>
       <c r="D369" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A370" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C370" t="s">
         <v>424</v>
       </c>
       <c r="D370" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A371" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C371" t="s">
         <v>424</v>
       </c>
       <c r="D371" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A372" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C372" t="s">
         <v>424</v>
       </c>
       <c r="D372" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A373" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C373" t="s">
         <v>424</v>
       </c>
       <c r="D373" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C374" t="s">
         <v>424</v>
       </c>
       <c r="D374" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C375" t="s">
         <v>424</v>
       </c>
       <c r="D375" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C376" t="s">
         <v>424</v>
       </c>
       <c r="D376" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A377" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C377" t="s">
         <v>424</v>
       </c>
       <c r="D377" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C378" t="s">
         <v>424</v>
       </c>
       <c r="D378" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C379" t="s">
         <v>424</v>
       </c>
       <c r="D379" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A380" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C380" t="s">
         <v>424</v>
       </c>
       <c r="D380" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C381" t="s">
         <v>424</v>
       </c>
       <c r="D381" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C382" t="s">
         <v>424</v>
       </c>
       <c r="D382" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C383" t="s">
         <v>424</v>
       </c>
       <c r="D383" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C384" t="s">
         <v>424</v>
       </c>
       <c r="D384" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A385" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C385" t="s">
         <v>424</v>
       </c>
       <c r="D385" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C386" t="s">
         <v>424</v>
       </c>
       <c r="D386" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A387" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C387" t="s">
         <v>424</v>
       </c>
       <c r="D387" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C388" t="s">
         <v>424</v>
       </c>
       <c r="D388" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A389" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C389" t="s">
         <v>424</v>
       </c>
       <c r="D389" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A390" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C390" t="s">
         <v>424</v>
       </c>
       <c r="D390" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A391" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C391" t="s">
         <v>424</v>
       </c>
       <c r="D391" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A392" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C392" t="s">
         <v>424</v>
       </c>
       <c r="D392" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C393" t="s">
         <v>424</v>
       </c>
       <c r="D393" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A394" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C394" t="s">
         <v>424</v>
       </c>
       <c r="D394" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A395" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C395" t="s">
         <v>424</v>
       </c>
       <c r="D395" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C396" t="s">
         <v>424</v>
       </c>
       <c r="D396" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A397" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C397" t="s">
         <v>424</v>
       </c>
       <c r="D397" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C398" t="s">
         <v>424</v>
       </c>
       <c r="D398" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C399" t="s">
         <v>424</v>
       </c>
       <c r="D399" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C400" t="s">
         <v>424</v>
       </c>
       <c r="D400" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A401" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C401" t="s">
         <v>424</v>
       </c>
       <c r="D401" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C402" t="s">
         <v>424</v>
       </c>
       <c r="D402" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A403" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C403" t="s">
         <v>424</v>
       </c>
       <c r="D403" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A404" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C404" t="s">
         <v>424</v>
       </c>
       <c r="D404" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A405" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C405" t="s">
         <v>424</v>
       </c>
       <c r="D405" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A406" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C406" t="s">
         <v>424</v>
       </c>
       <c r="D406" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C407" t="s">
         <v>424</v>
       </c>
       <c r="D407" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C408" t="s">
         <v>424</v>
       </c>
       <c r="D408" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C409" t="s">
         <v>424</v>
       </c>
       <c r="D409" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C410" t="s">
         <v>424</v>
       </c>
       <c r="D410" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C411" t="s">
         <v>424</v>
       </c>
       <c r="D411" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C412" t="s">
         <v>424</v>
       </c>
       <c r="D412" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A413" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C413" t="s">
         <v>424</v>
       </c>
       <c r="D413" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C414" t="s">
         <v>424</v>
       </c>
       <c r="D414" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A415" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C415" t="s">
         <v>424</v>
       </c>
       <c r="D415" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C416" t="s">
         <v>424</v>
       </c>
       <c r="D416" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C417" t="s">
         <v>424</v>
       </c>
       <c r="D417" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A418" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C418" t="s">
         <v>424</v>
       </c>
       <c r="D418" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C419" t="s">
         <v>424</v>
       </c>
       <c r="D419" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C420" t="s">
         <v>424</v>
       </c>
       <c r="D420" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C421" t="s">
         <v>424</v>
       </c>
       <c r="D421" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C422" t="s">
         <v>424</v>
       </c>
       <c r="D422" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C423" t="s">
         <v>424</v>
       </c>
       <c r="D423" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C424" t="s">
         <v>424</v>
       </c>
       <c r="D424" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A425" s="3" t="s">
-        <v>422</v>
+      <c r="A425" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="C425" t="s">
         <v>424</v>
@@ -7354,8 +7397,8 @@
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A426" s="3" t="s">
-        <v>423</v>
+      <c r="A426" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="C426" t="s">
         <v>424</v>
@@ -7366,7 +7409,7 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C427" t="s">
         <v>424</v>
@@ -7377,7 +7420,7 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C428" t="s">
         <v>424</v>
@@ -7388,7 +7431,7 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C429" t="s">
         <v>424</v>
@@ -7399,7 +7442,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C430" t="s">
         <v>424</v>
@@ -7410,7 +7453,7 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C431" t="s">
         <v>424</v>
@@ -7421,7 +7464,7 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C432" t="s">
         <v>424</v>
@@ -7432,7 +7475,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C433" t="s">
         <v>424</v>
@@ -7443,7 +7486,7 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A434" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C434" t="s">
         <v>424</v>
@@ -7454,7 +7497,7 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C435" t="s">
         <v>424</v>
@@ -7465,7 +7508,7 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C436" t="s">
         <v>424</v>
@@ -7476,7 +7519,7 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C437" t="s">
         <v>424</v>
@@ -7487,7 +7530,7 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="C438" t="s">
         <v>424</v>
@@ -7498,7 +7541,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="C439" t="s">
         <v>424</v>
@@ -7509,7 +7552,7 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C440" t="s">
         <v>424</v>
@@ -7520,7 +7563,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C441" t="s">
         <v>424</v>
@@ -7531,7 +7574,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C442" t="s">
         <v>424</v>
@@ -7542,7 +7585,7 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C443" t="s">
         <v>424</v>
@@ -7553,7 +7596,7 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C444" t="s">
         <v>424</v>
@@ -7564,7 +7607,7 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C445" t="s">
         <v>424</v>
@@ -7575,7 +7618,7 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C446" t="s">
         <v>424</v>
@@ -7586,7 +7629,7 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C447" t="s">
         <v>424</v>
@@ -7597,7 +7640,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A448" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C448" t="s">
         <v>424</v>
@@ -7608,7 +7651,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C449" t="s">
         <v>424</v>
@@ -7619,7 +7662,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C450" t="s">
         <v>424</v>
@@ -7630,7 +7673,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C451" t="s">
         <v>424</v>
@@ -7641,7 +7684,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C452" t="s">
         <v>424</v>
@@ -7652,7 +7695,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C453" t="s">
         <v>424</v>
@@ -7663,7 +7706,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A454" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C454" t="s">
         <v>424</v>
@@ -7674,7 +7717,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C455" t="s">
         <v>424</v>
@@ -7685,7 +7728,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A456" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C456" t="s">
         <v>424</v>
@@ -7696,7 +7739,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C457" t="s">
         <v>424</v>
@@ -7707,7 +7750,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C458" t="s">
         <v>424</v>
@@ -7718,7 +7761,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C459" t="s">
         <v>424</v>
@@ -7729,7 +7772,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C460" t="s">
         <v>424</v>
@@ -7740,7 +7783,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C461" t="s">
         <v>424</v>
@@ -7751,7 +7794,7 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A462" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C462" t="s">
         <v>424</v>
@@ -7762,7 +7805,7 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C463" t="s">
         <v>424</v>
@@ -7773,7 +7816,7 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C464" t="s">
         <v>424</v>
@@ -7784,7 +7827,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C465" t="s">
         <v>424</v>
@@ -7795,7 +7838,7 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C466" t="s">
         <v>424</v>
@@ -7806,7 +7849,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C467" t="s">
         <v>424</v>
@@ -7817,7 +7860,7 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C468" t="s">
         <v>424</v>
@@ -7828,7 +7871,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C469" t="s">
         <v>424</v>
@@ -7839,7 +7882,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A470" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C470" t="s">
         <v>424</v>
@@ -7850,7 +7893,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C471" t="s">
         <v>424</v>
@@ -7861,7 +7904,7 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C472" t="s">
         <v>424</v>
@@ -7872,7 +7915,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C473" t="s">
         <v>424</v>
@@ -7883,7 +7926,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C474" t="s">
         <v>424</v>
@@ -7894,7 +7937,7 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C475" t="s">
         <v>424</v>
@@ -7905,7 +7948,7 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C476" t="s">
         <v>424</v>
@@ -7916,7 +7959,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C477" t="s">
         <v>424</v>
@@ -7927,7 +7970,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C478" t="s">
         <v>424</v>
@@ -7938,7 +7981,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A479" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C479" t="s">
         <v>424</v>
@@ -7949,7 +7992,7 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C480" t="s">
         <v>424</v>
@@ -7960,7 +8003,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C481" t="s">
         <v>424</v>
@@ -7971,7 +8014,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C482" t="s">
         <v>424</v>
@@ -7982,7 +8025,7 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C483" t="s">
         <v>424</v>
@@ -7993,7 +8036,7 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C484" t="s">
         <v>424</v>
@@ -8004,7 +8047,7 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C485" t="s">
         <v>424</v>
@@ -8015,7 +8058,7 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C486" t="s">
         <v>424</v>
@@ -8026,7 +8069,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C487" t="s">
         <v>424</v>
@@ -8037,7 +8080,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C488" t="s">
         <v>424</v>
@@ -8048,7 +8091,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C489" t="s">
         <v>424</v>
@@ -8059,7 +8102,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C490" t="s">
         <v>424</v>
@@ -8070,7 +8113,7 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C491" t="s">
         <v>424</v>
@@ -8081,7 +8124,7 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C492" t="s">
         <v>424</v>
@@ -8092,7 +8135,7 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C493" t="s">
         <v>424</v>
@@ -8103,7 +8146,7 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C494" t="s">
         <v>424</v>
@@ -8114,7 +8157,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C495" t="s">
         <v>424</v>
@@ -8125,7 +8168,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C496" t="s">
         <v>424</v>
@@ -8136,7 +8179,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C497" t="s">
         <v>424</v>
@@ -8147,7 +8190,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A498" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C498" t="s">
         <v>424</v>
@@ -8158,7 +8201,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A499" s="2" t="s">
-        <v>311</v>
+        <v>555</v>
       </c>
       <c r="C499" t="s">
         <v>424</v>
@@ -8169,7 +8212,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C500" t="s">
         <v>424</v>
@@ -8180,7 +8223,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C501" t="s">
         <v>424</v>
@@ -8191,7 +8234,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C502" t="s">
         <v>424</v>
@@ -8202,7 +8245,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C503" t="s">
         <v>424</v>
@@ -8213,7 +8256,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A504" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C504" t="s">
         <v>424</v>
@@ -8224,7 +8267,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C505" t="s">
         <v>424</v>
@@ -8235,7 +8278,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A506" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C506" t="s">
         <v>424</v>
@@ -8246,7 +8289,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C507" t="s">
         <v>424</v>
@@ -8257,7 +8300,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A508" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C508" t="s">
         <v>424</v>
@@ -8268,7 +8311,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A509" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C509" t="s">
         <v>424</v>
@@ -8279,7 +8322,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A510" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C510" t="s">
         <v>424</v>
@@ -8290,7 +8333,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A511" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C511" t="s">
         <v>424</v>
@@ -8301,7 +8344,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C512" t="s">
         <v>424</v>
@@ -8312,7 +8355,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C513" t="s">
         <v>424</v>
@@ -8323,7 +8366,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C514" t="s">
         <v>424</v>
@@ -8334,7 +8377,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C515" t="s">
         <v>424</v>
@@ -8345,7 +8388,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A516" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C516" t="s">
         <v>424</v>
@@ -8356,7 +8399,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C517" t="s">
         <v>424</v>
@@ -8367,7 +8410,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A518" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C518" t="s">
         <v>424</v>
@@ -8378,7 +8421,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C519" t="s">
         <v>424</v>
@@ -8389,7 +8432,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C520" t="s">
         <v>424</v>
@@ -8400,7 +8443,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C521" t="s">
         <v>424</v>
@@ -8411,7 +8454,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C522" t="s">
         <v>424</v>
@@ -8422,7 +8465,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C523" t="s">
         <v>424</v>
@@ -8433,7 +8476,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C524" t="s">
         <v>424</v>
@@ -8444,7 +8487,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C525" t="s">
         <v>424</v>
@@ -8455,7 +8498,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C526" t="s">
         <v>424</v>
@@ -8466,7 +8509,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C527" t="s">
         <v>424</v>
@@ -8477,7 +8520,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C528" t="s">
         <v>424</v>
@@ -8488,7 +8531,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C529" t="s">
         <v>424</v>
@@ -8499,7 +8542,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C530" t="s">
         <v>424</v>
@@ -8510,7 +8553,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C531" t="s">
         <v>424</v>
@@ -8521,7 +8564,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C532" t="s">
         <v>424</v>
@@ -8532,7 +8575,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C533" t="s">
         <v>424</v>
@@ -8543,7 +8586,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A534" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C534" t="s">
         <v>424</v>
@@ -8554,7 +8597,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C535" t="s">
         <v>424</v>
@@ -8565,7 +8608,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A536" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C536" t="s">
         <v>424</v>
@@ -8576,7 +8619,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C537" t="s">
         <v>424</v>
@@ -8587,7 +8630,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A538" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C538" t="s">
         <v>424</v>
@@ -8598,7 +8641,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C539" t="s">
         <v>424</v>
@@ -8609,7 +8652,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A540" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C540" t="s">
         <v>424</v>
@@ -8620,7 +8663,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C541" t="s">
         <v>424</v>
@@ -8631,7 +8674,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A542" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C542" t="s">
         <v>424</v>
@@ -8642,7 +8685,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C543" t="s">
         <v>424</v>
@@ -8653,7 +8696,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A544" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C544" t="s">
         <v>424</v>
@@ -8664,7 +8707,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C545" t="s">
         <v>424</v>
@@ -8675,7 +8718,7 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A546" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C546" t="s">
         <v>424</v>
@@ -8686,7 +8729,7 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C547" t="s">
         <v>424</v>
@@ -8697,7 +8740,7 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C548" t="s">
         <v>424</v>
@@ -8708,7 +8751,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C549" t="s">
         <v>424</v>
@@ -8719,7 +8762,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A550" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C550" t="s">
         <v>424</v>
@@ -8730,7 +8773,7 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C551" t="s">
         <v>424</v>
@@ -8741,7 +8784,7 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A552" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C552" t="s">
         <v>424</v>
@@ -8752,7 +8795,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A553" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C553" t="s">
         <v>424</v>
@@ -8763,7 +8806,7 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C554" t="s">
         <v>424</v>
@@ -8774,7 +8817,7 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C555" t="s">
         <v>424</v>
@@ -8785,7 +8828,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A556" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C556" t="s">
         <v>424</v>
@@ -8796,7 +8839,7 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A557" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C557" t="s">
         <v>424</v>
@@ -8807,7 +8850,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A558" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C558" t="s">
         <v>424</v>
@@ -8818,7 +8861,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A559" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C559" t="s">
         <v>424</v>
@@ -8829,7 +8872,7 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A560" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C560" t="s">
         <v>424</v>
@@ -8840,7 +8883,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A561" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C561" t="s">
         <v>424</v>
@@ -8851,7 +8894,7 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A562" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C562" t="s">
         <v>424</v>
@@ -8862,7 +8905,7 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C563" t="s">
         <v>424</v>
@@ -8873,7 +8916,7 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A564" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C564" t="s">
         <v>424</v>
@@ -8884,7 +8927,7 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
-        <v>618</v>
+        <v>426</v>
       </c>
       <c r="C565" t="s">
         <v>424</v>
@@ -8895,7 +8938,7 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A566" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C566" t="s">
         <v>424</v>
@@ -8906,7 +8949,7 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C567" t="s">
         <v>424</v>
@@ -8917,7 +8960,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
-        <v>426</v>
+        <v>623</v>
       </c>
       <c r="C568" t="s">
         <v>424</v>
@@ -8928,7 +8971,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A569" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C569" t="s">
         <v>424</v>
@@ -8939,7 +8982,7 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C570" t="s">
         <v>424</v>
@@ -8950,7 +8993,7 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C571" t="s">
         <v>424</v>
@@ -8961,7 +9004,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A572" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C572" t="s">
         <v>424</v>
@@ -8972,7 +9015,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A573" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C573" t="s">
         <v>424</v>
@@ -8983,7 +9026,7 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C574" t="s">
         <v>424</v>
@@ -8994,7 +9037,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C575" t="s">
         <v>424</v>
@@ -9005,7 +9048,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A576" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C576" t="s">
         <v>424</v>
@@ -9016,7 +9059,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C577" t="s">
         <v>424</v>
@@ -9027,7 +9070,7 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A578" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C578" t="s">
         <v>424</v>
@@ -9038,7 +9081,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C579" t="s">
         <v>424</v>
@@ -9049,7 +9092,7 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C580" t="s">
         <v>424</v>
@@ -9060,7 +9103,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C581" t="s">
         <v>424</v>
@@ -9071,7 +9114,7 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A582" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C582" t="s">
         <v>424</v>
@@ -9082,7 +9125,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C583" t="s">
         <v>424</v>
@@ -9093,7 +9136,7 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A584" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C584" t="s">
         <v>424</v>
@@ -9104,7 +9147,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A585" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C585" t="s">
         <v>424</v>
@@ -9115,7 +9158,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A586" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C586" t="s">
         <v>424</v>
@@ -9126,7 +9169,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C587" t="s">
         <v>424</v>
@@ -9137,7 +9180,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C588" t="s">
         <v>424</v>
@@ -9148,7 +9191,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A589" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C589" t="s">
         <v>424</v>
@@ -9159,7 +9202,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A590" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C590" t="s">
         <v>424</v>
@@ -9170,7 +9213,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C591" t="s">
         <v>424</v>
@@ -9181,7 +9224,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A592" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C592" t="s">
         <v>424</v>
@@ -9192,7 +9235,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A593" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C593" t="s">
         <v>424</v>
@@ -9203,7 +9246,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A594" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C594" t="s">
         <v>424</v>
@@ -9214,7 +9257,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C595" t="s">
         <v>424</v>
@@ -9225,7 +9268,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C596" t="s">
         <v>424</v>
@@ -9236,7 +9279,7 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C597" t="s">
         <v>424</v>
@@ -9247,7 +9290,7 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A598" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C598" t="s">
         <v>424</v>
@@ -9258,7 +9301,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A599" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C599" t="s">
         <v>424</v>
@@ -9269,7 +9312,7 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A600" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C600" t="s">
         <v>424</v>
@@ -9280,7 +9323,7 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C601" t="s">
         <v>424</v>
@@ -9291,7 +9334,7 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A602" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C602" t="s">
         <v>424</v>
@@ -9302,7 +9345,7 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C603" t="s">
         <v>424</v>
@@ -9313,7 +9356,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A604" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C604" t="s">
         <v>424</v>
@@ -9324,7 +9367,7 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C605" t="s">
         <v>424</v>
@@ -9335,7 +9378,7 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A606" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C606" t="s">
         <v>424</v>
@@ -9346,7 +9389,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A607" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C607" t="s">
         <v>424</v>
@@ -9357,7 +9400,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A608" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C608" t="s">
         <v>424</v>
@@ -9368,7 +9411,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C609" t="s">
         <v>424</v>
@@ -9379,7 +9422,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A610" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C610" t="s">
         <v>424</v>
@@ -9390,7 +9433,7 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C611" t="s">
         <v>424</v>
@@ -9401,7 +9444,7 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C612" t="s">
         <v>424</v>
@@ -9412,7 +9455,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C613" t="s">
         <v>424</v>
@@ -9423,7 +9466,7 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A614" s="2" t="s">
-        <v>666</v>
+        <v>458</v>
       </c>
       <c r="C614" t="s">
         <v>424</v>
@@ -9434,7 +9477,7 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A615" s="2" t="s">
-        <v>667</v>
+        <v>427</v>
       </c>
       <c r="C615" t="s">
         <v>424</v>
@@ -9445,7 +9488,7 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A616" s="2" t="s">
-        <v>668</v>
+        <v>428</v>
       </c>
       <c r="C616" t="s">
         <v>424</v>
@@ -9456,7 +9499,7 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
-        <v>458</v>
+        <v>669</v>
       </c>
       <c r="C617" t="s">
         <v>424</v>
@@ -9467,7 +9510,7 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C618" t="s">
         <v>424</v>
@@ -9478,7 +9521,7 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A619" s="2" t="s">
-        <v>428</v>
+        <v>670</v>
       </c>
       <c r="C619" t="s">
         <v>424</v>
@@ -9489,7 +9532,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
-        <v>669</v>
+        <v>430</v>
       </c>
       <c r="C620" t="s">
         <v>424</v>
@@ -9500,7 +9543,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C621" t="s">
         <v>424</v>
@@ -9511,7 +9554,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
-        <v>670</v>
+        <v>432</v>
       </c>
       <c r="C622" t="s">
         <v>424</v>
@@ -9522,7 +9565,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C623" t="s">
         <v>424</v>
@@ -9533,7 +9576,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A624" s="2" t="s">
-        <v>431</v>
+        <v>671</v>
       </c>
       <c r="C624" t="s">
         <v>424</v>
@@ -9544,7 +9587,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A625" s="2" t="s">
-        <v>432</v>
+        <v>672</v>
       </c>
       <c r="C625" t="s">
         <v>424</v>
@@ -9555,7 +9598,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
-        <v>433</v>
+        <v>673</v>
       </c>
       <c r="C626" t="s">
         <v>424</v>
@@ -9566,7 +9609,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A627" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C627" t="s">
         <v>424</v>
@@ -9577,7 +9620,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C628" t="s">
         <v>424</v>
@@ -9588,7 +9631,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C629" t="s">
         <v>424</v>
@@ -9599,7 +9642,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C630" t="s">
         <v>424</v>
@@ -9610,7 +9653,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A631" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C631" t="s">
         <v>424</v>
@@ -9621,7 +9664,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C632" t="s">
         <v>424</v>
@@ -9632,7 +9675,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C633" t="s">
         <v>424</v>
@@ -9643,7 +9686,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A634" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C634" t="s">
         <v>424</v>
@@ -9654,7 +9697,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C635" t="s">
         <v>424</v>
@@ -9665,7 +9708,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C636" t="s">
         <v>424</v>
@@ -9676,7 +9719,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C637" t="s">
         <v>424</v>
@@ -9687,7 +9730,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A638" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C638" t="s">
         <v>424</v>
@@ -9698,7 +9741,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A639" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C639" t="s">
         <v>424</v>
@@ -9709,7 +9752,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A640" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C640" t="s">
         <v>424</v>
@@ -9720,7 +9763,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C641" t="s">
         <v>424</v>
@@ -9731,7 +9774,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C642" t="s">
         <v>424</v>
@@ -9742,7 +9785,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A643" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C643" t="s">
         <v>424</v>
@@ -9753,7 +9796,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C644" t="s">
         <v>424</v>
@@ -9764,7 +9807,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
-        <v>176</v>
+        <v>692</v>
       </c>
       <c r="C645" t="s">
         <v>424</v>
@@ -9775,7 +9818,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C646" t="s">
         <v>424</v>
@@ -9786,7 +9829,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>181</v>
+        <v>694</v>
       </c>
       <c r="C647" t="s">
         <v>424</v>
@@ -9797,7 +9840,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="C648" t="s">
         <v>424</v>
@@ -9808,7 +9851,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C649" t="s">
         <v>424</v>
@@ -9819,7 +9862,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C650" t="s">
         <v>424</v>
@@ -9830,7 +9873,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="C651" t="s">
         <v>424</v>
@@ -9841,7 +9884,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="C652" t="s">
         <v>424</v>
@@ -9852,7 +9895,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C653" t="s">
         <v>424</v>
@@ -9863,7 +9906,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A654" s="2" t="s">
-        <v>189</v>
+        <v>701</v>
       </c>
       <c r="C654" t="s">
         <v>424</v>
@@ -9874,7 +9917,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A655" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C655" t="s">
         <v>424</v>
@@ -9885,7 +9928,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C656" t="s">
         <v>424</v>
@@ -9896,7 +9939,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A657" s="2" t="s">
-        <v>221</v>
+        <v>704</v>
       </c>
       <c r="C657" t="s">
         <v>424</v>
@@ -9907,7 +9950,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C658" t="s">
         <v>424</v>
@@ -9918,7 +9961,7 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A659" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="C659" t="s">
         <v>424</v>
@@ -9929,7 +9972,7 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="C660" t="s">
         <v>424</v>
@@ -9940,7 +9983,7 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="C661" t="s">
         <v>424</v>
@@ -9951,7 +9994,7 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C662" t="s">
         <v>424</v>
@@ -9962,7 +10005,7 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="C663" t="s">
         <v>424</v>
@@ -9973,7 +10016,7 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="C664" t="s">
         <v>424</v>
@@ -9984,7 +10027,7 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="C665" t="s">
         <v>424</v>
@@ -9995,7 +10038,7 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="C666" t="s">
         <v>424</v>
@@ -10006,7 +10049,7 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A667" s="2" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C667" t="s">
         <v>424</v>
@@ -10017,7 +10060,7 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C668" t="s">
         <v>424</v>
@@ -10028,7 +10071,7 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C669" t="s">
         <v>424</v>
@@ -10039,7 +10082,7 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C670" t="s">
         <v>424</v>
@@ -10050,7 +10093,7 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A671" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="C671" t="s">
         <v>424</v>
@@ -10061,7 +10104,7 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>712</v>
+        <v>434</v>
       </c>
       <c r="C672" t="s">
         <v>424</v>
@@ -10072,7 +10115,7 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
-        <v>713</v>
+        <v>435</v>
       </c>
       <c r="C673" t="s">
         <v>424</v>
@@ -10083,7 +10126,7 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>714</v>
+        <v>436</v>
       </c>
       <c r="C674" t="s">
         <v>424</v>
@@ -10094,7 +10137,7 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>715</v>
+        <v>437</v>
       </c>
       <c r="C675" t="s">
         <v>424</v>
@@ -10105,7 +10148,7 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="C676" t="s">
         <v>424</v>
@@ -10116,7 +10159,7 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C677" t="s">
         <v>424</v>
@@ -10127,7 +10170,7 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A678" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C678" t="s">
         <v>424</v>
@@ -10138,7 +10181,7 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C679" t="s">
         <v>424</v>
@@ -10149,7 +10192,7 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
-        <v>434</v>
+        <v>723</v>
       </c>
       <c r="C680" t="s">
         <v>424</v>
@@ -10160,7 +10203,7 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A681" s="2" t="s">
-        <v>435</v>
+        <v>724</v>
       </c>
       <c r="C681" t="s">
         <v>424</v>
@@ -10171,7 +10214,7 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
-        <v>436</v>
+        <v>725</v>
       </c>
       <c r="C682" t="s">
         <v>424</v>
@@ -10182,7 +10225,7 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A683" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C683" t="s">
         <v>424</v>
@@ -10193,7 +10236,7 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A684" s="2" t="s">
-        <v>719</v>
+        <v>439</v>
       </c>
       <c r="C684" t="s">
         <v>424</v>
@@ -10204,7 +10247,7 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
-        <v>720</v>
+        <v>440</v>
       </c>
       <c r="C685" t="s">
         <v>424</v>
@@ -10215,7 +10258,7 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="C686" t="s">
         <v>424</v>
@@ -10226,7 +10269,7 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="C687" t="s">
         <v>424</v>
@@ -10237,7 +10280,7 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C688" t="s">
         <v>424</v>
@@ -10248,7 +10291,7 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="C689" t="s">
         <v>424</v>
@@ -10259,7 +10302,7 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C690" t="s">
         <v>424</v>
@@ -10270,7 +10313,7 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
-        <v>438</v>
+        <v>731</v>
       </c>
       <c r="C691" t="s">
         <v>424</v>
@@ -10281,7 +10324,7 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A692" s="2" t="s">
-        <v>439</v>
+        <v>732</v>
       </c>
       <c r="C692" t="s">
         <v>424</v>
@@ -10292,7 +10335,7 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A693" s="2" t="s">
-        <v>440</v>
+        <v>733</v>
       </c>
       <c r="C693" t="s">
         <v>424</v>
@@ -10303,7 +10346,7 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A694" s="2" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="C694" t="s">
         <v>424</v>
@@ -10314,7 +10357,7 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A695" s="2" t="s">
-        <v>727</v>
+        <v>441</v>
       </c>
       <c r="C695" t="s">
         <v>424</v>
@@ -10325,7 +10368,7 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A696" s="2" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="C696" t="s">
         <v>424</v>
@@ -10336,7 +10379,7 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A697" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="C697" t="s">
         <v>424</v>
@@ -10347,7 +10390,7 @@
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="C698" t="s">
         <v>424</v>
@@ -10358,7 +10401,7 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A699" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="C699" t="s">
         <v>424</v>
@@ -10369,7 +10412,7 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="C700" t="s">
         <v>424</v>
@@ -10380,7 +10423,7 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A701" s="2" t="s">
-        <v>733</v>
+        <v>442</v>
       </c>
       <c r="C701" t="s">
         <v>424</v>
@@ -10391,7 +10434,7 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C702" t="s">
         <v>424</v>
@@ -10402,7 +10445,7 @@
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A703" s="2" t="s">
-        <v>441</v>
+        <v>741</v>
       </c>
       <c r="C703" t="s">
         <v>424</v>
@@ -10413,7 +10456,7 @@
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
-        <v>735</v>
+        <v>443</v>
       </c>
       <c r="C704" t="s">
         <v>424</v>
@@ -10424,7 +10467,7 @@
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C705" t="s">
         <v>424</v>
@@ -10435,7 +10478,7 @@
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
-        <v>737</v>
+        <v>444</v>
       </c>
       <c r="C706" t="s">
         <v>424</v>
@@ -10446,7 +10489,7 @@
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A707" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="C707" t="s">
         <v>424</v>
@@ -10457,7 +10500,7 @@
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
-        <v>739</v>
+        <v>492</v>
       </c>
       <c r="C708" t="s">
         <v>424</v>
@@ -10468,7 +10511,7 @@
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C709" t="s">
         <v>424</v>
@@ -10479,7 +10522,7 @@
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
-        <v>740</v>
+        <v>446</v>
       </c>
       <c r="C710" t="s">
         <v>424</v>
@@ -10490,7 +10533,7 @@
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A711" s="2" t="s">
-        <v>741</v>
+        <v>447</v>
       </c>
       <c r="C711" t="s">
         <v>424</v>
@@ -10501,7 +10544,7 @@
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C712" t="s">
         <v>424</v>
@@ -10512,7 +10555,7 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A713" s="2" t="s">
-        <v>742</v>
+        <v>449</v>
       </c>
       <c r="C713" t="s">
         <v>424</v>
@@ -10523,7 +10566,7 @@
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A714" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C714" t="s">
         <v>424</v>
@@ -10534,7 +10577,7 @@
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A715" s="2" t="s">
-        <v>743</v>
+        <v>491</v>
       </c>
       <c r="C715" t="s">
         <v>424</v>
@@ -10545,7 +10588,7 @@
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A716" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C716" t="s">
         <v>424</v>
@@ -10556,7 +10599,7 @@
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A717" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C717" t="s">
         <v>424</v>
@@ -10567,7 +10610,7 @@
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A718" s="2" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="C718" t="s">
         <v>424</v>
@@ -10578,7 +10621,7 @@
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A719" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C719" t="s">
         <v>424</v>
@@ -10589,7 +10632,7 @@
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A720" s="2" t="s">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="C720" t="s">
         <v>424</v>
@@ -10600,7 +10643,7 @@
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A721" s="2" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="C721" t="s">
         <v>424</v>
@@ -10611,7 +10654,7 @@
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A722" s="2" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="C722" t="s">
         <v>424</v>
@@ -10622,7 +10665,7 @@
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A723" s="2" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="C723" t="s">
         <v>424</v>
@@ -10633,7 +10676,7 @@
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A724" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C724" t="s">
         <v>424</v>
@@ -10644,7 +10687,7 @@
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A725" s="2" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="C725" t="s">
         <v>424</v>
@@ -10655,7 +10698,7 @@
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A726" s="2" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C726" t="s">
         <v>424</v>
@@ -10666,7 +10709,7 @@
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A727" s="2" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="C727" t="s">
         <v>424</v>
@@ -10677,7 +10720,7 @@
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A728" s="2" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C728" t="s">
         <v>424</v>
@@ -10688,7 +10731,7 @@
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A729" s="2" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C729" t="s">
         <v>424</v>
@@ -10699,7 +10742,7 @@
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A730" s="2" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C730" t="s">
         <v>424</v>
@@ -10710,7 +10753,7 @@
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A731" s="2" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C731" t="s">
         <v>424</v>
@@ -10721,7 +10764,7 @@
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A732" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C732" t="s">
         <v>424</v>
@@ -10732,7 +10775,7 @@
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A733" s="2" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="C733" t="s">
         <v>424</v>
@@ -10743,7 +10786,7 @@
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A734" s="2" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="C734" t="s">
         <v>424</v>
@@ -10754,7 +10797,7 @@
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A735" s="2" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="C735" t="s">
         <v>424</v>
@@ -10765,7 +10808,7 @@
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A736" s="2" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="C736" t="s">
         <v>424</v>
@@ -10774,9 +10817,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A737" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C737" t="s">
         <v>424</v>
@@ -10785,9 +10828,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A738" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C738" t="s">
         <v>424</v>
@@ -10796,9 +10839,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A739" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C739" t="s">
         <v>424</v>
@@ -10807,21 +10850,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A740" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C740" t="s">
-        <v>424</v>
-      </c>
-      <c r="D740" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A741" s="2" t="s">
-        <v>454</v>
-      </c>
+    <row r="741" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C741" t="s">
         <v>424</v>
       </c>
@@ -10829,9 +10858,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A742" s="2" t="s">
-        <v>455</v>
+    <row r="742" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A742" t="s">
+        <v>744</v>
       </c>
       <c r="C742" t="s">
         <v>424</v>
@@ -10840,9 +10869,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A743" s="2" t="s">
-        <v>456</v>
+    <row r="743" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A743" t="s">
+        <v>750</v>
       </c>
       <c r="C743" t="s">
         <v>424</v>
@@ -10850,10 +10879,13 @@
       <c r="D743" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A744" s="2" t="s">
-        <v>457</v>
+      <c r="E743" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A744" t="s">
+        <v>745</v>
       </c>
       <c r="C744" t="s">
         <v>424</v>
@@ -10862,9 +10894,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A745" s="2" t="s">
-        <v>476</v>
+    <row r="745" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A745" t="s">
+        <v>746</v>
       </c>
       <c r="C745" t="s">
         <v>424</v>
@@ -10873,9 +10905,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A746" s="2" t="s">
-        <v>475</v>
+    <row r="746" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A746" t="s">
+        <v>747</v>
       </c>
       <c r="C746" t="s">
         <v>424</v>
@@ -10884,9 +10916,9 @@
         <v>425</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A747" s="2" t="s">
-        <v>474</v>
+    <row r="747" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A747" t="s">
+        <v>748</v>
       </c>
       <c r="C747" t="s">
         <v>424</v>
@@ -10895,12 +10927,45 @@
         <v>425</v>
       </c>
     </row>
+    <row r="748" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A748" t="s">
+        <v>105</v>
+      </c>
+      <c r="C748" t="s">
+        <v>424</v>
+      </c>
+      <c r="D748" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="749" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A749" t="s">
+        <v>751</v>
+      </c>
+      <c r="C749" t="s">
+        <v>424</v>
+      </c>
+      <c r="D749" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A750" t="s">
+        <v>749</v>
+      </c>
+      <c r="C750" t="s">
+        <v>424</v>
+      </c>
+      <c r="D750" t="s">
+        <v>425</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A747" xr:uid="{A05EE52F-6B9B-9646-8D2F-C9D94D87C781}"/>
+  <autoFilter ref="A1:A739" xr:uid="{A05EE52F-6B9B-9646-8D2F-C9D94D87C781}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D226">
     <sortCondition ref="A1:A226"/>
   </sortState>
-  <conditionalFormatting sqref="A906:A1048576 A1:A747">
+  <conditionalFormatting sqref="A898:A1048576 A1:A739">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ClimOO material/materials for implementations /ClimOO Vocabulary.xlsx
+++ b/ClimOO material/materials for implementations /ClimOO Vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/f.u./Desktop/ClimOO-Ontology/ClimOO material/materials for implementations /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644F0F0F-C9D3-7445-AEBA-43BD9FEE45D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B034F02-DB40-A545-B432-80EF90361BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29520" yWindow="4280" windowWidth="28800" windowHeight="16380" xr2:uid="{CB153552-6711-0040-AB62-F0CB02156726}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="868">
   <si>
     <t>Terms</t>
   </si>
@@ -2607,6 +2607,42 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>optical property</t>
+  </si>
+  <si>
+    <t>electromagnetic radiation property</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>grey</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>yellow</t>
   </si>
 </sst>
 </file>
@@ -2686,17 +2722,7 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3057,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05EE52F-6B9B-9646-8D2F-C9D94D87C781}">
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="82.5" style="1" bestFit="1" customWidth="1"/>
@@ -12514,18 +12540,150 @@
         <v>855</v>
       </c>
     </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A862" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C862" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A863" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C863" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A864" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C864" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A865" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C865" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A866" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C866" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A867" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A868" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C868" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A869" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C869" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A870" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C870" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A871" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C871" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A872" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B872" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C872" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A873" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="C873" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C226">
     <sortCondition ref="A1:A226"/>
   </sortState>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A895:A1048576 A1:A739">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D831:D836">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
